--- a/register_scan_20260313.xlsx
+++ b/register_scan_20260313.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,14 +65,8 @@
       <color rgb="002E4057"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -114,11 +108,6 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -146,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -179,9 +168,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -572,7 +558,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  11:03    Registers: 256    PASS: 65    FAIL: 3    N/I: 185</t>
+          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  11:29    Registers: 256    PASS: 70    FAIL: 0    N/I: 185</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1289,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>NOOP</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1980,7 +1966,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1990,17 +1976,17 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>0x0000</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>MISMATCH(0x1282)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>expected 0x0000 got 0x1282</t>
+          <t xml:space="preserve">Fatal status (write-to-clear; read-only </t>
         </is>
       </c>
     </row>
@@ -2022,7 +2008,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -2032,17 +2018,17 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>0x0000</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>MISMATCH(0x1287)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>expected 0x0000 got 0x1287</t>
+          <t>Warning status (write-to-clear; read-onl</t>
         </is>
       </c>
     </row>
@@ -2647,12 +2633,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Power/GRID</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -2662,17 +2648,17 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>XE</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>write returned execution error</t>
+          <t>Laser channel – read-only in test (write</t>
         </is>
       </c>
     </row>
@@ -5004,7 +4990,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -5014,17 +5000,17 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>XE</t>
-        </is>
-      </c>
-      <c r="G108" s="11" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>write returned execution error</t>
+          <t>Grid 2 – MHz offset (read-only in test)</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6712,7 @@
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
@@ -6736,17 +6722,17 @@
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>0x0019</t>
-        </is>
-      </c>
-      <c r="G149" s="12" t="inlineStr">
-        <is>
-          <t>MISMATCH(0x0001)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>expected 0x0019 got 0x0001</t>
+          <t>Mfr: TEC current – live ADC readback (ov</t>
         </is>
       </c>
     </row>

--- a/register_scan_20260313.xlsx
+++ b/register_scan_20260313.xlsx
@@ -558,7 +558,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  11:29    Registers: 256    PASS: 70    FAIL: 0    N/I: 185</t>
+          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  11:44    Registers: 256    PASS: 70    FAIL: 0    N/I: 185</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>MinFreq_THz</t>
+          <t>LF1Min_THz</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Min lasing frequency – THz part</t>
+          <t>Min lasing freq – THz (Table A)</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>MaxFreq_THz</t>
+          <t>LF1Max_THz</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>Max lasing frequency – THz part</t>
+          <t>Max lasing freq – THz (Table A)</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>MinFreq_G10</t>
+          <t>FTFR_MHz</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Min lasing frequency – GHz×10 part</t>
+          <t>Fine tune freq range (MHz)</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>MinFreq_G10</t>
+          <t>MinFreq_THz</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>Min lasing frequency – GHz×10 part</t>
+          <t>Min lasing freq – THz (cap97)</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>MaxFreq_THz</t>
+          <t>MinFreq_G10</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Max lasing frequency – THz part</t>
+          <t>Min lasing freq – GHz×10 (cap97)</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>MaxFreq_G10</t>
+          <t>MaxFreq_THz</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>Max lasing frequency – GHz×10 part</t>
+          <t>Max lasing freq – THz (cap97)</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>MinPower</t>
+          <t>MaxFreq_G10</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>Min optical power (dBm×100)</t>
+          <t>Max lasing freq – GHz×10 (cap97)</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>Last channel freq – GHz×10</t>
+          <t>Last channel freq – GHz×10 (note: uses c</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>CaseTemp</t>
+          <t>DitherCtrl</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>Case/PCB temperature (°C×100)</t>
+          <t>Dither waveform/enable control</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>V1_rdac</t>
+          <t>V1_lut</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>Mfr: Ring-1 voltage read-back (×100 → V)</t>
+          <t>Mfr: Ring-1 V – LUT setpoint (÷100 → V)</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>V2_rdac</t>
+          <t>V2_lut</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>Mfr: Ring-2 voltage read-back (×100 → V)</t>
+          <t>Mfr: Ring-2 V – LUT setpoint (÷100 → V)</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>V3_rdac</t>
+          <t>V3_lut</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>Mfr: Phase voltage read-back (×100 → V)</t>
+          <t>Mfr: Phase V – LUT setpoint (÷100 → V)</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>Gain_rdac</t>
+          <t>Gain_lut</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="H135" s="8" t="inlineStr">
         <is>
-          <t>Mfr: Gain bias read-back (×100 → V)</t>
+          <t>Mfr: Gain bias – LUT setpoint (÷100)</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>SOA_rdac</t>
+          <t>SOA_lut</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>Mfr: SOA current read-back (×100 → V)</t>
+          <t>Mfr: SOA current – LUT setpoint (÷100)</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>Temp_rdac</t>
+          <t>Temp_lut</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>Mfr: Temperature read-back (×100)</t>
+          <t>Mfr: TEC temp – LUT setpoint (raw)</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Power_PD</t>
+          <t>MPD_lut</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>Mfr: Main power detector (MPD) ADC</t>
+          <t>Mfr: Main PD – LUT setpoint</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>Etalon_PD</t>
+          <t>WLPD_lut</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
-          <t>Mfr: Etalon PD (WLPD) ADC</t>
+          <t>Mfr: Etalon PD – LUT setpoint</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>WM_PD</t>
+          <t>WMPD_lut</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>Mfr: Wavelength monitor PD (WMPD) ADC</t>
+          <t>Mfr: WM PD – LUT setpoint</t>
         </is>
       </c>
     </row>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>WM_PD_alias</t>
+          <t>WMPD_adc</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>0x000a</t>
+          <t>0x0000</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>Mfr: WMPD alias (= 0x88)</t>
+          <t>Mfr: WM PD – live ADC (÷10 = mV)</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Etalon_PD_alias</t>
+          <t>WLPD_adc</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>0x0000</t>
+          <t>0x000a</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="H142" s="6" t="inlineStr">
         <is>
-          <t>Mfr: WLPD alias (= 0x87)</t>
+          <t>Mfr: Etalon PD – live ADC (÷10 = mV)</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>Power_PD_alias</t>
+          <t>MPD_adc</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>Mfr: MPD alias (= 0x86)</t>
+          <t>Mfr: Main PD – live ADC (÷10 = mV)</t>
         </is>
       </c>
     </row>

--- a/register_scan_20260313.xlsx
+++ b/register_scan_20260313.xlsx
@@ -558,7 +558,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  11:44    Registers: 256    PASS: 70    FAIL: 0    N/I: 185</t>
+          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  11:55    Registers: 256    PASS: 70    FAIL: 0    N/I: 185</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>0x0000</t>
+          <t>0x000a</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">

--- a/register_scan_20260313.xlsx
+++ b/register_scan_20260313.xlsx
@@ -558,7 +558,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  11:55    Registers: 256    PASS: 70    FAIL: 0    N/I: 185</t>
+          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  12:55    Registers: 256    PASS: 70    FAIL: 0    N/I: 185</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>0x1b59</t>
+          <t>0x1b94</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>0x0001</t>
+          <t>0x003c</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>0x0001</t>
+          <t>0x003c</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>Laser channel (low word, alias)</t>
+          <t>Laser channel – ch60 (first populated LU</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>0x000a</t>
+          <t>0x0000</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>0x000a</t>
+          <t>0x0000</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">

--- a/register_scan_20260313.xlsx
+++ b/register_scan_20260313.xlsx
@@ -558,7 +558,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  12:55    Registers: 256    PASS: 70    FAIL: 0    N/I: 185</t>
+          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  15:03    Registers: 256    PASS: 82    FAIL: 0    N/I: 173</t>
         </is>
       </c>
     </row>
@@ -4259,86 +4259,86 @@
       </c>
     </row>
     <row r="91" ht="13" customHeight="1">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>0x57</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H91" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Currents</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>AEA</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>0x0008</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>9.8.1: Module currents array (mA×10) via</t>
         </is>
       </c>
     </row>
     <row r="92" ht="13" customHeight="1">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>0x58</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Temps</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>AEA</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>0x0004</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>9.8.2: Diode and case temperatures (°C×1</t>
         </is>
       </c>
     </row>
@@ -4360,363 +4360,363 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>9.8.3: Dither ctrl – bits[5:4]=waveform,</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="13" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>0x5A</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>DitherRate</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>9.8.3: Dither rate (valid 10–200, defaul</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="13" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>0x5B</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>DitherFreq</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>9.8.3: Dither frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="13" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>DitherAmp</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>9.8.3: Dither amplitude (0–1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="13" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>TBTFL</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>0xfe0c</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>0xfe0c</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>9.8.4: Thermal boundary low limit (°C×10</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="13" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>0x5E</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>TBTFH</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>0x1b58</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>0x1b58</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>9.8.4: Thermal boundary high limit (°C×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="13" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>0x5F</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>FAgeTh</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>9.8.6: Fatal age threshold (%EOL, 0=disa</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="13" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>WAgeTh</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>9.8.6: Warning age threshold (%EOL, 0=di</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="13" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>0x0000</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>Dither waveform/enable control</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="13" customHeight="1">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>0x5A</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="13" customHeight="1">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>0x5B</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H95" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="13" customHeight="1">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>0x5C</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H96" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="13" customHeight="1">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>0x5D</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H97" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="13" customHeight="1">
-      <c r="A98" s="9" t="inlineStr">
-        <is>
-          <t>0x5E</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H98" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="13" customHeight="1">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>0x5F</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H99" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="13" customHeight="1">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>0x60</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H100" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="13" customHeight="1">
-      <c r="A101" s="9" t="inlineStr">
-        <is>
-          <t>0x61</t>
-        </is>
-      </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E101" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H101" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>0xcf2c</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>9.8.6: Module age (%EOL, read-only)</t>
         </is>
       </c>
     </row>
@@ -4763,86 +4763,86 @@
       </c>
     </row>
     <row r="103" ht="13" customHeight="1">
-      <c r="A103" s="9" t="inlineStr">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>0x63</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H103" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>FFreqTh2</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>9.5 ext: Fatal frequency threshold 2</t>
         </is>
       </c>
     </row>
     <row r="104" ht="13" customHeight="1">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>0x64</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G104" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H104" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>WFreqTh2</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>0x0032</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>9.5 ext: Warning frequency threshold 2</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>0x0000</t>
+          <t>0x000a</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>0x0000</t>
+          <t>0x000a</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">

--- a/register_scan_20260313.xlsx
+++ b/register_scan_20260313.xlsx
@@ -558,7 +558,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  15:03    Registers: 256    PASS: 82    FAIL: 0    N/I: 173</t>
+          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  15:24    Registers: 256    PASS: 82    FAIL: 0    N/I: 173</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>0x1b94</t>
+          <t>0x1bbd</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>0x0000</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>0x0000</t>
+          <t>0x0032</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>0x003c</t>
+          <t>0x0065</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">

--- a/register_scan_20260313.xlsx
+++ b/register_scan_20260313.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +65,14 @@
       <color rgb="002E4057"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +114,11 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -135,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -168,6 +179,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -558,7 +572,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  15:24    Registers: 256    PASS: 82    FAIL: 0    N/I: 173</t>
+          <t>Port: /dev/ttyUSB0    Date: 2026-03-13  16:41    Registers: 256    PASS: 84    FAIL: 1    N/I: 169</t>
         </is>
       </c>
     </row>
@@ -627,7 +641,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>0x0000</t>
+          <t>0x0001</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -1289,12 +1303,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>NOOP</t>
+          <t>EA_DATA</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1304,17 +1318,17 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>XE</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>write returned execution error</t>
+          <t>Extended access data read port (write re</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2830,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x01f4</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -2826,7 +2840,7 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Channel grid spacing (GHz×10)</t>
+          <t>Channel grid spacing (GHz×10); 500=50 GH</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3403,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>LF1Min_THz</t>
+          <t>OOP</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -3404,17 +3418,17 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Min lasing freq – THz (Table A)</t>
+          <t>write returned execution error</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3445,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>LF1Max_THz</t>
+          <t>CTemp</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -3446,17 +3460,17 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>Max lasing freq – THz (Table A)</t>
+          <t>write returned execution error</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3991,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>MinFreq_THz</t>
+          <t>OPSL</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4002,7 +4016,7 @@
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>Min lasing freq – THz (cap97)</t>
+          <t xml:space="preserve">Min optical output power setpoint (0.01 </t>
         </is>
       </c>
     </row>
@@ -4019,7 +4033,7 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>MinFreq_G10</t>
+          <t>OPSH</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -4044,7 +4058,7 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Min lasing freq – GHz×10 (cap97)</t>
+          <t xml:space="preserve">Max optical output power setpoint (0.01 </t>
         </is>
       </c>
     </row>
@@ -4061,7 +4075,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>MaxFreq_THz</t>
+          <t>LFL1</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4086,7 +4100,7 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>Max lasing freq – THz (cap97)</t>
+          <t>Min lasing freq – THz part (cap97) §9.7</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4117,7 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>MaxFreq_G10</t>
+          <t>LFL2</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4128,7 +4142,7 @@
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>Max lasing freq – GHz×10 (cap97)</t>
+          <t>Min lasing freq – GHz×10 part (cap97) §9</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4159,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>LastFreq_THz</t>
+          <t>LFH1</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -4155,7 +4169,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>0x00c1</t>
+          <t>0x00c6</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -4170,7 +4184,7 @@
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>Last channel freq – THz</t>
+          <t>Max lasing freq – THz part (cap97) §9.7</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4201,7 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>LastFreq_G10</t>
+          <t>LFH2</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -4197,7 +4211,7 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>0x1bbd</t>
+          <t>0x11d0</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -4212,7 +4226,7 @@
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>Last channel freq – GHz×10 (note: uses c</t>
+          <t>Max lasing freq – GHz×10 part (cap97) §9</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4898,7 @@
       </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>Laser channel (high word)</t>
+          <t>Laser channel high word (staged; committ</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4915,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>ChannelL</t>
+          <t>Grid2</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -4911,12 +4925,12 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>0x0065</t>
+          <t>0x003c</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>0x003c</t>
+          <t>0x0000</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -4926,7 +4940,7 @@
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>Laser channel – ch60 (first populated LU</t>
+          <t>Fine grid spacing (MHz, signed) §9.6 ext</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4982,7 @@
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>First channel freq – MHz part</t>
+          <t>First channel freq – MHz fine part</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4999,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Grid2_MHz</t>
+          <t>LF3</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -5010,133 +5024,133 @@
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>Grid 2 – MHz offset (read-only in test)</t>
+          <t>Laser freq – MHz fine part (LF3, read-on</t>
         </is>
       </c>
     </row>
     <row r="109" ht="13" customHeight="1">
-      <c r="A109" s="9" t="inlineStr">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>0x69</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H109" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>LFL3</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>Min lasing freq – MHz fine part (read-on</t>
         </is>
       </c>
     </row>
     <row r="110" ht="13" customHeight="1">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>0x6A</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H110" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>LFH3</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>Max lasing freq – MHz fine part (read-on</t>
         </is>
       </c>
     </row>
     <row r="111" ht="13" customHeight="1">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>0x6B</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F111" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G111" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H111" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>LGrid2</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>Grid step – MHz fine part (read-only) §9</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6227,7 @@
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>0x00fa</t>
+          <t>0x000a</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
@@ -6381,7 +6395,7 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>0x000a</t>
+          <t>0x0000</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -6423,7 +6437,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>0x000a</t>
+          <t>0x0000</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -6465,7 +6479,7 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>0x000a</t>
+          <t>0x0000</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -6712,7 +6726,7 @@
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
@@ -6722,59 +6736,59 @@
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t>MISMATCH(0x0001)</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>Mfr: TEC current – live ADC readback (ov</t>
+          <t>expected 0x0000 got 0x0001</t>
         </is>
       </c>
     </row>
     <row r="150" ht="13" customHeight="1">
-      <c r="A150" s="9" t="inlineStr">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t>0x92</t>
         </is>
       </c>
-      <c r="B150" s="9" t="inlineStr">
+      <c r="B150" s="4" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="C150" s="9" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D150" s="9" t="inlineStr">
-        <is>
-          <t>N/I</t>
-        </is>
-      </c>
-      <c r="E150" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F150" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G150" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H150" s="10" t="inlineStr">
-        <is>
-          <t>Not implemented / reserved</t>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>DirectCtrl</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>Mfr: Direct control mode (write 0x4142/0</t>
         </is>
       </c>
     </row>
